--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>title</t>
   </si>
@@ -50,13 +50,25 @@
   </si>
   <si>
     <t>awards</t>
+  </si>
+  <si>
+    <t>Sample-efficient non-Gaussian noise reduction in gravitational wave data via learnable wavelets</t>
+  </si>
+  <si>
+    <t>Arush Pimpalkar, Digvijay Wadekar, Mark Ho-Yeuk Cheung, and Emanuele Berti</t>
+  </si>
+  <si>
+    <t>assets/images/publications/WaveletNet.png</t>
+  </si>
+  <si>
+    <t>Paper|https://arxiv.org/abs/2601.14326</t>
+  </si>
+  <si>
+    <t>WaveletNet is a wavelet-based neural network designed to identify and mitigate non-Gaussian noise in gravitational wave data by learning optimal wavelet representations of glitches. Exploiting the wavelet-like structure of high-mass black hole–mimicking glitches, it is significantly more sample-efficient than traditional CNNs. The method is used modularly to assign a noise-related score that can be added to existing pipeline detection statistics. Applied to the IAS-HM search pipeline, WaveletNet improves the sensitive search volume by up to 15% for high-mass, asymmetric binaries.</t>
   </si>
   <si>
     <t>Improving gravitational wave search sensitivity with TIER:
 Trigger Inference using Extended strain Representation</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Digvijay Wadekar, Arush Pimpalkar, Mark Ho-Yeuk Cheung, Benjamin Wandel, Emanuele Berti, Ajit Kumar Mehta, Tejaswi Venumadhav, Javier Roulet, Tousif Islam, Barak Zackay, Jonathan Mushkin and Matias Zaldarriaga</t>
@@ -158,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -169,10 +181,13 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
@@ -492,21 +507,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="62.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="55.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="32.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="59.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="57.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="9" width="80.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="9" width="104.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="9" width="47.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="9" width="30.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="10" width="62.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="21.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="55.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="32.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="11" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="59.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="57.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="10" width="80.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="10" width="104.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="10" width="47.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="10" width="30.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5" customFormat="1" s="1">
@@ -547,175 +562,197 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="102.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="99">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="5">
+        <v>2025</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="6">
-        <v>2025</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="42" customFormat="1" s="1">
-      <c r="A3" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="102.75" customFormat="1" s="1">
+      <c r="A3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="6">
+      <c r="I3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="70.5" customFormat="1" s="1">
+      <c r="A4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7">
         <v>2024</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
+      <c r="F4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="22.5" customFormat="1" s="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="22.5" customFormat="1" s="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="151.5" customFormat="1" s="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="38.25" customFormat="1" s="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="87" customFormat="1" s="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="119.25" customFormat="1" s="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="167.25" customFormat="1" s="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="39" customFormat="1" s="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="22.5" customFormat="1" s="1">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="22.5" customFormat="1" s="1">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="22.5" customFormat="1" s="1">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="22.5" customFormat="1" s="1">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="22.5" customFormat="1" s="1">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="167.25" customFormat="1" s="1">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="39" customFormat="1" s="1">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -58,7 +58,7 @@
     <t>Arush Pimpalkar, Digvijay Wadekar, Mark Ho-Yeuk Cheung, and Emanuele Berti</t>
   </si>
   <si>
-    <t>assets/images/publications/WaveletNet.png</t>
+    <t>/assets/images/publications/WaveletNet.png</t>
   </si>
   <si>
     <t>Paper|https://arxiv.org/abs/2601.14326</t>
@@ -572,7 +572,7 @@
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="5">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -1,133 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="projects"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="projects" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>section</t>
-  </si>
-  <si>
-    <t>authors</t>
-  </si>
-  <si>
-    <t>journal</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>image</t>
-  </si>
-  <si>
-    <t>image_alt</t>
-  </si>
-  <si>
-    <t>links</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>themes</t>
-  </si>
-  <si>
-    <t>awards</t>
-  </si>
-  <si>
-    <t>Sample-efficient non-Gaussian noise reduction in gravitational wave data via learnable wavelets</t>
-  </si>
-  <si>
-    <t>Arush Pimpalkar, Digvijay Wadekar, Mark Ho-Yeuk Cheung, and Emanuele Berti</t>
-  </si>
-  <si>
-    <t>/assets/images/publications/WaveletNet.png</t>
-  </si>
-  <si>
-    <t>Paper|https://arxiv.org/abs/2601.14326</t>
-  </si>
-  <si>
-    <t>WaveletNet is a wavelet-based neural network designed to identify and mitigate non-Gaussian noise in gravitational wave data by learning optimal wavelet representations of glitches. Exploiting the wavelet-like structure of high-mass black hole–mimicking glitches, it is significantly more sample-efficient than traditional CNNs. The method is used modularly to assign a noise-related score that can be added to existing pipeline detection statistics. Applied to the IAS-HM search pipeline, WaveletNet improves the sensitive search volume by up to 15% for high-mass, asymmetric binaries.</t>
-  </si>
-  <si>
-    <t>Improving gravitational wave search sensitivity with TIER:
-Trigger Inference using Extended strain Representation</t>
-  </si>
-  <si>
-    <t>Digvijay Wadekar, Arush Pimpalkar, Mark Ho-Yeuk Cheung, Benjamin Wandel, Emanuele Berti, Ajit Kumar Mehta, Tejaswi Venumadhav, Javier Roulet, Tousif Islam, Barak Zackay, Jonathan Mushkin and Matias Zaldarriaga</t>
-  </si>
-  <si>
-    <t>/assets/images/publications/TIER.png</t>
-  </si>
-  <si>
-    <t>Paper|https://inspirehep.net/literature/2945008</t>
-  </si>
-  <si>
-    <t>We introduce TIER, a machine learning framework that uses extra strain data around candidate signals to make gravitational-wave searches more sensitive—boosting performance by up to 20% and helping reveal fainter, high-mass, and unequal-mass events that might otherwise go unnoticed.</t>
-  </si>
-  <si>
-    <t>ML</t>
-  </si>
-  <si>
-    <t>Gravitational Wave Transient Searches Using Machine Learning</t>
-  </si>
-  <si>
-    <t>Arush Pimpalkar, Bhooshan Gadre</t>
-  </si>
-  <si>
-    <t>/assets/images/publications/still_thinking.png</t>
-  </si>
-  <si>
-    <t>Developed deep learning models for gravitational wave detection and parameter estimation, replacing traditional matched filtering for improved efficiency. Achieved 97.25% accuracy in waveform classification and low MSEs in predicting chirp mass, SNR, and time of peak waveform.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -171,51 +84,113 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -503,256 +478,349 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="10" width="62.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="55.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="32.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="11" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="59.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="57.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="80.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="10" width="104.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="10" width="47.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="10" width="30.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col width="62.57642857142857" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
+    <col width="21.14785714285714" bestFit="1" customWidth="1" style="10" min="2" max="2"/>
+    <col width="55.86214285714286" bestFit="1" customWidth="1" style="10" min="3" max="3"/>
+    <col width="32.29071428571429" bestFit="1" customWidth="1" style="10" min="4" max="4"/>
+    <col width="10.86214285714286" bestFit="1" customWidth="1" style="11" min="5" max="5"/>
+    <col width="59.14785714285715" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
+    <col width="57.57642857142857" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
+    <col width="80.86214285714286" bestFit="1" customWidth="1" style="10" min="8" max="8"/>
+    <col width="104.005" bestFit="1" customWidth="1" style="10" min="9" max="9"/>
+    <col width="47.29071428571429" bestFit="1" customWidth="1" style="10" min="10" max="10"/>
+    <col width="30.57642857142857" bestFit="1" customWidth="1" style="10" min="11" max="11"/>
+    <col width="12.43357142857143" bestFit="1" customWidth="1" style="10" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5" customFormat="1" s="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="99">
-      <c r="A2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5">
+    <row r="1" ht="22.5" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>authors</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>image_alt</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>links</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>themes</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>awards</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="99" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A Physics-Accurate Digital Twin and System Identification Framework for the Caltech 40 m Prototype Input Mode Cleaner</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Arush Pimpalkar, Michael Padilla, Nathan Holland, Rana Adhikari</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>2026</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="102.75" customFormat="1" s="1">
-      <c r="A3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>/assets/images/publications/Caltech_IMC.png</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Diagram of the Caltech 40 m Input Mode Cleaner digital twin</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>The Caltech 40 m Prototype is a scaled-down test-bed for the technology inside LIGO's gravitational-wave detectors. This project builds a digital twin of its Input Mode Cleaner, a triangular optical cavity of three suspended mirrors that cleans up the laser beam before it reaches the main interferometer. The simulation traces a disturbance end to end: ground vibrations shake the suspensions, the mirrors move, that motion imprints itself on the laser light, and the digital control system pushes back. Every stage is validated against measurements from the real instrument rather than assumed, so the twin reproduces how the machine actually behaves. The result is a testbed for trying out control schemes and noise-reduction ideas in software before running them on hardware.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Instrumentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="102.75" customFormat="1" customHeight="1" s="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Sample-efficient non-Gaussian noise reduction in gravitational wave data via learnable wavelets</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Arush Pimpalkar, Digvijay Wadekar, Mark Ho-Yeuk Cheung, and Emanuele Berti</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>/assets/images/publications/WaveletNet.png</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Paper|https://journals.aps.org/prd/abstract/10.1103/33k8-331b</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>WaveletNet is a wavelet-based neural network designed to identify and mitigate non-Gaussian noise in gravitational wave data by learning optimal wavelet representations of glitches. Exploiting the wavelet-like structure of high-mass black hole–mimicking glitches, it is significantly more sample-efficient than traditional CNNs. The method is used modularly to assign a noise-related score that can be added to existing pipeline detection statistics. Applied to the IAS-HM search pipeline, WaveletNet improves the sensitive search volume by up to 15% for high-mass, asymmetric binaries.</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="70.5" customFormat="1" customHeight="1" s="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Improving gravitational wave search sensitivity with TIER:
+Trigger Inference using Extended strain Representation</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Digvijay Wadekar, Arush Pimpalkar, Mark Ho-Yeuk Cheung, Benjamin Wandel, Emanuele Berti, Ajit Kumar Mehta, Tejaswi Venumadhav, Javier Roulet, Tousif Islam, Barak Zackay, Jonathan Mushkin and Matias Zaldarriaga</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="70.5" customFormat="1" s="1">
-      <c r="A4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>/assets/images/publications/TIER.png</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Paper|https://inspirehep.net/literature/2945008</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>We introduce TIER, a machine learning framework that uses extra strain data around candidate signals to make gravitational-wave searches more sensitive—boosting performance by up to 20% and helping reveal fainter, high-mass, and unequal-mass events that might otherwise go unnoticed.</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="22.5" customFormat="1" customHeight="1" s="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Gravitational Wave Transient Searches Using Machine Learning</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Arush Pimpalkar, Bhooshan Gadre</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="22.5" customFormat="1" s="1">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="22.5" customFormat="1" s="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="22.5" customFormat="1" s="1">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="22.5" customFormat="1" s="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="22.5" customFormat="1" s="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="22.5" customFormat="1" s="1">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="167.25" customFormat="1" s="1">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="39" customFormat="1" s="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>/assets/images/publications/still_thinking.png</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Developed deep learning models for gravitational wave detection and parameter estimation, replacing traditional matched filtering for improved efficiency. Achieved 97.25% accuracy in waveform classification and low MSEs in predicting chirp mass, SNR, and time of peak waveform.</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="22.5" customFormat="1" customHeight="1" s="1">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="22.5" customFormat="1" customHeight="1" s="1">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="22.5" customFormat="1" customHeight="1" s="1">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="22.5" customFormat="1" customHeight="1" s="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="22.5" customFormat="1" customHeight="1" s="1">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+    </row>
+    <row r="11" ht="167.25" customFormat="1" customHeight="1" s="1">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+    </row>
+    <row r="12" ht="39" customFormat="1" customHeight="1" s="1">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
